--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133418296</v>
       </c>
       <c r="B2" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>133418295</v>
       </c>
       <c r="B3" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133418296</v>
       </c>
       <c r="B2" t="n">
-        <v>92520</v>
+        <v>92528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133418296</v>
       </c>
       <c r="B2" t="n">
-        <v>92528</v>
+        <v>92519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>133418295</v>
       </c>
       <c r="B3" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133418296</v>
       </c>
       <c r="B2" t="n">
-        <v>92519</v>
+        <v>92529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>133418295</v>
       </c>
       <c r="B3" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133418296</v>
       </c>
       <c r="B2" t="n">
-        <v>92529</v>
+        <v>92531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>133418295</v>
       </c>
       <c r="B3" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133418296</v>
       </c>
       <c r="B2" t="n">
-        <v>92531</v>
+        <v>92546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>133418295</v>
       </c>
       <c r="B3" t="n">
-        <v>80474</v>
+        <v>80488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133418296</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133418295</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,49 +796,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133418295</v>
+        <v>135630423</v>
       </c>
       <c r="B3" t="n">
-        <v>80488</v>
+        <v>92588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Utanede, Jmt</t>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595734</v>
+        <v>595779</v>
       </c>
       <c r="R3" t="n">
-        <v>6980391</v>
+        <v>6980341</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +877,2999 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135630423</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135630418</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92016</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>595739</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6980351</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630418</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135630431</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92016</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>595737</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6980352</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630431</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135630429</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83262</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595758</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6980345</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630429</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135630420</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89260</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595756</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6980359</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630420</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135630415</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92073</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595737</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6980325</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630415</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135630426</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91979</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595781</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6980342</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630426</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135630410</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79411</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595670</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6980347</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630410</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135630413</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79411</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>595729</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6980314</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630413</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135630419</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79411</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>595746</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6980358</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630419</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135630427</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79411</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>595793</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6980314</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630427</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135630406</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83398</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>595655</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6980382</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630406</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135630409</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83398</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>595672</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6980349</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630409</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135630412</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83398</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>595709</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6980326</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630412</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135630414</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83398</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>595737</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6980313</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630414</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135630407</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>595651</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6980382</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630407</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133418295</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Utanede, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>595734</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6980391</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/133418295</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135630422</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80526</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>595765</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6980357</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630422</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135630424</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80526</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>595779</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6980341</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630424</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135630430</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80526</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>595750</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6980347</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630430</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135630432</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80526</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>595722</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6980388</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630432</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135630417</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80531</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>595729</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6980345</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630417</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135630425</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80531</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>595778</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6980340</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630425</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135630408</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>595645</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6980367</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630408</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135630416</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>595737</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6980323</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630416</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135630411</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99159</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>595704</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6980323</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630411</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135630428</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99159</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>595756</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6980338</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630428</t>
         </is>
       </c>
     </row>
@@ -914,6 +3877,32 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135630423</v>
       </c>
       <c r="B3" t="n">
-        <v>92588</v>
+        <v>92615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>595779</v>
       </c>
       <c r="R3" t="n">
-        <v>6980341</v>
+        <v>6980342</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,7 +916,7 @@
         <v>135630418</v>
       </c>
       <c r="B4" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135630431</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>135630429</v>
       </c>
       <c r="B6" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>135630420</v>
       </c>
       <c r="B7" t="n">
-        <v>89260</v>
+        <v>89287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135630415</v>
       </c>
       <c r="B8" t="n">
-        <v>92073</v>
+        <v>92100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135630426</v>
       </c>
       <c r="B9" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>135630410</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135630413</v>
       </c>
       <c r="B11" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>135630419</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135630427</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>135630406</v>
       </c>
       <c r="B14" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>135630409</v>
       </c>
       <c r="B15" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135630412</v>
       </c>
       <c r="B16" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135630414</v>
       </c>
       <c r="B17" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>135630407</v>
       </c>
       <c r="B18" t="n">
-        <v>79497</v>
+        <v>79524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135630422</v>
       </c>
       <c r="B20" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>135630424</v>
       </c>
       <c r="B21" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>595779</v>
       </c>
       <c r="R21" t="n">
-        <v>6980341</v>
+        <v>6980342</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
         <v>135630430</v>
       </c>
       <c r="B22" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>135630432</v>
       </c>
       <c r="B23" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135630417</v>
       </c>
       <c r="B24" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>135630425</v>
       </c>
       <c r="B25" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>135630411</v>
       </c>
       <c r="B28" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>135630428</v>
       </c>
       <c r="B29" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,49 +796,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133418295</v>
+        <v>135630423</v>
       </c>
       <c r="B3" t="n">
-        <v>80488</v>
+        <v>92620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Utanede, Jmt</t>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595734</v>
+        <v>595779</v>
       </c>
       <c r="R3" t="n">
-        <v>6980391</v>
+        <v>6980341</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +877,2999 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135630423</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135630418</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>595739</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6980351</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630418</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135630431</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>595737</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6980352</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630431</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135630429</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83292</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595758</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6980345</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630429</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135630420</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89290</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595756</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6980359</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630420</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135630415</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92105</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595737</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6980325</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630415</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135630426</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595781</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6980342</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630426</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135630410</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595670</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6980347</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630410</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135630413</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>595729</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6980314</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630413</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135630419</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>595746</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6980358</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630419</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135630427</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>595793</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6980314</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630427</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135630406</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>595655</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6980382</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630406</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135630409</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>595672</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6980349</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630409</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135630412</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>595709</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6980326</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630412</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135630414</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>595737</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6980313</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630414</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135630407</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79527</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>595651</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6980382</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630407</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133418295</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Utanede, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>595734</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6980391</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/133418295</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135630422</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>595765</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6980357</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630422</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135630424</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>595779</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6980341</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630424</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135630430</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>595750</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6980347</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630430</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135630432</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>595722</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6980388</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630432</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135630417</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>595729</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6980345</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630417</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135630425</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>595778</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6980340</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630425</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135630408</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>595645</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6980367</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630408</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135630416</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>595737</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6980323</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630416</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135630411</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>595704</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6980323</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630411</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135630428</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sundmyrbäcken, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>595756</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6980338</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135630428</t>
         </is>
       </c>
     </row>
@@ -914,6 +3877,32 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135630423</v>
       </c>
       <c r="B3" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>595779</v>
       </c>
       <c r="R3" t="n">
-        <v>6980341</v>
+        <v>6980342</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,7 +916,7 @@
         <v>135630418</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135630431</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>135630420</v>
       </c>
       <c r="B7" t="n">
-        <v>89290</v>
+        <v>89292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135630415</v>
       </c>
       <c r="B8" t="n">
-        <v>92105</v>
+        <v>92107</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135630426</v>
       </c>
       <c r="B9" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>595779</v>
       </c>
       <c r="R21" t="n">
-        <v>6980341</v>
+        <v>6980342</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3674,7 +3674,7 @@
         <v>135630411</v>
       </c>
       <c r="B28" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>135630428</v>
       </c>
       <c r="B29" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -834,7 +834,7 @@
         <v>595779</v>
       </c>
       <c r="R3" t="n">
-        <v>6980342</v>
+        <v>6980341</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2910,7 +2910,7 @@
         <v>595779</v>
       </c>
       <c r="R21" t="n">
-        <v>6980342</v>
+        <v>6980341</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -834,7 +834,7 @@
         <v>595779</v>
       </c>
       <c r="R3" t="n">
-        <v>6980341</v>
+        <v>6980342</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2910,7 +2910,7 @@
         <v>595779</v>
       </c>
       <c r="R21" t="n">
-        <v>6980341</v>
+        <v>6980342</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135630423</v>
       </c>
       <c r="B3" t="n">
-        <v>92622</v>
+        <v>92637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135630418</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135630431</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>135630429</v>
       </c>
       <c r="B6" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>135630420</v>
       </c>
       <c r="B7" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135630415</v>
       </c>
       <c r="B8" t="n">
-        <v>92107</v>
+        <v>92121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135630426</v>
       </c>
       <c r="B9" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>135630410</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135630413</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>135630419</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135630427</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>135630406</v>
       </c>
       <c r="B14" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>135630409</v>
       </c>
       <c r="B15" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135630412</v>
       </c>
       <c r="B16" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135630414</v>
       </c>
       <c r="B17" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>135630407</v>
       </c>
       <c r="B18" t="n">
-        <v>79527</v>
+        <v>79529</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135630422</v>
       </c>
       <c r="B20" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>135630424</v>
       </c>
       <c r="B21" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135630430</v>
       </c>
       <c r="B22" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>135630432</v>
       </c>
       <c r="B23" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135630417</v>
       </c>
       <c r="B24" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>135630425</v>
       </c>
       <c r="B25" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>135630408</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135630416</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>135630411</v>
       </c>
       <c r="B28" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>135630428</v>
       </c>
       <c r="B29" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135630423</v>
       </c>
       <c r="B3" t="n">
-        <v>92637</v>
+        <v>92638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135630418</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135630431</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>135630429</v>
       </c>
       <c r="B6" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>135630420</v>
       </c>
       <c r="B7" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135630415</v>
       </c>
       <c r="B8" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135630426</v>
       </c>
       <c r="B9" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>135630410</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135630413</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>135630419</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135630427</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>135630406</v>
       </c>
       <c r="B14" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>135630409</v>
       </c>
       <c r="B15" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135630412</v>
       </c>
       <c r="B16" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135630414</v>
       </c>
       <c r="B17" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>135630407</v>
       </c>
       <c r="B18" t="n">
-        <v>79529</v>
+        <v>79530</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135630422</v>
       </c>
       <c r="B20" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>135630424</v>
       </c>
       <c r="B21" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135630430</v>
       </c>
       <c r="B22" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>135630432</v>
       </c>
       <c r="B23" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135630417</v>
       </c>
       <c r="B24" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>135630425</v>
       </c>
       <c r="B25" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>135630411</v>
       </c>
       <c r="B28" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>135630428</v>
       </c>
       <c r="B29" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135630423</v>
       </c>
       <c r="B3" t="n">
-        <v>92638</v>
+        <v>92639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135630418</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135630431</v>
       </c>
       <c r="B5" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>135630420</v>
       </c>
       <c r="B7" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135630415</v>
       </c>
       <c r="B8" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135630426</v>
       </c>
       <c r="B9" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>135630411</v>
       </c>
       <c r="B28" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>135630428</v>
       </c>
       <c r="B29" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135630423</v>
       </c>
       <c r="B3" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>595779</v>
       </c>
       <c r="R3" t="n">
-        <v>6980341</v>
+        <v>6980342</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,7 +916,7 @@
         <v>135630418</v>
       </c>
       <c r="B4" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135630431</v>
       </c>
       <c r="B5" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>135630429</v>
       </c>
       <c r="B6" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>135630420</v>
       </c>
       <c r="B7" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135630415</v>
       </c>
       <c r="B8" t="n">
-        <v>92123</v>
+        <v>92124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135630426</v>
       </c>
       <c r="B9" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>135630410</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135630413</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>135630419</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135630427</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>135630406</v>
       </c>
       <c r="B14" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>135630409</v>
       </c>
       <c r="B15" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135630412</v>
       </c>
       <c r="B16" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135630414</v>
       </c>
       <c r="B17" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>135630407</v>
       </c>
       <c r="B18" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135630422</v>
       </c>
       <c r="B20" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>135630424</v>
       </c>
       <c r="B21" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>595779</v>
       </c>
       <c r="R21" t="n">
-        <v>6980341</v>
+        <v>6980342</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
         <v>135630430</v>
       </c>
       <c r="B22" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>135630432</v>
       </c>
       <c r="B23" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135630417</v>
       </c>
       <c r="B24" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>135630425</v>
       </c>
       <c r="B25" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>135630408</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135630416</v>
       </c>
       <c r="B27" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>135630411</v>
       </c>
       <c r="B28" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>135630428</v>
       </c>
       <c r="B29" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 14696-2022 artfynd.xlsx
+++ b/artfynd/A 14696-2022 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135630423</v>
       </c>
       <c r="B3" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>595779</v>
       </c>
       <c r="R3" t="n">
-        <v>6980342</v>
+        <v>6980341</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,7 +916,7 @@
         <v>135630418</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135630431</v>
       </c>
       <c r="B5" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>135630429</v>
       </c>
       <c r="B6" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>135630420</v>
       </c>
       <c r="B7" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135630415</v>
       </c>
       <c r="B8" t="n">
-        <v>92124</v>
+        <v>92130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135630426</v>
       </c>
       <c r="B9" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>135630410</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135630413</v>
       </c>
       <c r="B11" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>135630419</v>
       </c>
       <c r="B12" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135630427</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>135630406</v>
       </c>
       <c r="B14" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>135630409</v>
       </c>
       <c r="B15" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135630412</v>
       </c>
       <c r="B16" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135630414</v>
       </c>
       <c r="B17" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>135630407</v>
       </c>
       <c r="B18" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>135630422</v>
       </c>
       <c r="B20" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>135630424</v>
       </c>
       <c r="B21" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>595779</v>
       </c>
       <c r="R21" t="n">
-        <v>6980342</v>
+        <v>6980341</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
         <v>135630430</v>
       </c>
       <c r="B22" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>135630432</v>
       </c>
       <c r="B23" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135630417</v>
       </c>
       <c r="B24" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>135630425</v>
       </c>
       <c r="B25" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>135630408</v>
       </c>
       <c r="B26" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135630416</v>
       </c>
       <c r="B27" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>135630411</v>
       </c>
       <c r="B28" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>135630428</v>
       </c>
       <c r="B29" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
